--- a/order/订仓装箱单模板.xlsx
+++ b/order/订仓装箱单模板.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\老张沙特物流订仓网站\albb-order-site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\老张沙特物流订仓网站\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="51">
   <si>
     <t>一家专注中东市场的国际物流企业（双清包税到门 / 或到港 / 或到机场，海运 + 空运，任君选择）</t>
   </si>
@@ -49,15 +49,9 @@
     <t>Shipping way 运输方式：</t>
   </si>
   <si>
-    <t>空运到门/海运到门/空运到机场/海运到港口</t>
-  </si>
-  <si>
     <t>是否需要单独报关：</t>
   </si>
   <si>
-    <t>是 / 否</t>
-  </si>
-  <si>
     <t>SHIPPER DETAILS（发件人资料）</t>
   </si>
   <si>
@@ -67,10 +61,10 @@
     <t>COMPANY NAME (公司名):</t>
   </si>
   <si>
+    <t>ADDRESS (地址):</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>ADDRESS (地址):</t>
   </si>
   <si>
     <t>短地址 
@@ -101,6 +95,10 @@
 英文名称</t>
   </si>
   <si>
+    <t>SKU
+（FBA必填）</t>
+  </si>
+  <si>
     <t>QUANTITY
 数量 (数)</t>
   </si>
@@ -163,6 +161,33 @@
   </si>
   <si>
     <t>型号</t>
+  </si>
+  <si>
+    <t>太阳能摄像头</t>
+  </si>
+  <si>
+    <t>SOLAR CAMERA</t>
+  </si>
+  <si>
+    <t>五金+塑料</t>
+  </si>
+  <si>
+    <t>监控</t>
+  </si>
+  <si>
+    <t>纸箱</t>
+  </si>
+  <si>
+    <t>带电</t>
+  </si>
+  <si>
+    <t>不带</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>样板请删除</t>
   </si>
   <si>
     <t>Total</t>
@@ -190,7 +215,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,13 +275,6 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -403,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,12 +460,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -615,7 +627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -664,6 +676,19 @@
       <bottom style="thin">
         <color rgb="FF999999"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -797,67 +822,70 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -872,77 +900,74 @@
     <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -992,27 +1017,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1069,6 +1098,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1362,59 +1396,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:20">
+    <row r="1" ht="20" customHeight="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:20">
+    <row r="2" ht="24" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:20">
-      <c r="K3" s="3" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:22">
+      <c r="L3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:20">
+    <row r="4" ht="22" customHeight="1" spans="1:22">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="9"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="8"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -1423,19 +1454,20 @@
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:20">
+    <row r="5" ht="22" customHeight="1" spans="1:22">
       <c r="A5" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -1446,25 +1478,22 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:20">
+    <row r="6" ht="22" customHeight="1" spans="1:22">
       <c r="A6" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="7"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="6"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
@@ -1473,25 +1502,24 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:20">
+    <row r="7" ht="22" customHeight="1" spans="1:22">
       <c r="A7" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="7"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="6"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
@@ -1500,21 +1528,22 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
     </row>
-    <row r="8" ht="49" customHeight="1" spans="1:20">
+    <row r="8" ht="49" customHeight="1" spans="1:22">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="14"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
@@ -1523,25 +1552,24 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="1:20">
+    <row r="9" ht="22" customHeight="1" spans="1:22">
       <c r="A9" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="D9" s="6"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -1550,25 +1578,24 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
     </row>
-    <row r="10" ht="22" customHeight="1" spans="1:20">
+    <row r="10" ht="22" customHeight="1" spans="1:22">
       <c r="A10" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="D10" s="6"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="6"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -1577,23 +1604,22 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
     </row>
-    <row r="11" ht="22" customHeight="1" spans="1:20">
+    <row r="11" ht="22" customHeight="1" spans="1:22">
       <c r="A11" s="11"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="D11" s="6"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="6"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
@@ -1602,1028 +1628,558 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
     </row>
-    <row r="12" ht="46" customHeight="1" spans="1:20">
+    <row r="12" ht="46" customHeight="1" spans="1:22">
       <c r="A12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="D12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="E12" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="F12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="G12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="H12" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="I12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="J12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="K12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="L12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="N12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="O12" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="P12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="16" t="s">
+      <c r="Q12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="P12" s="16" t="s">
+      <c r="R12" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="Q12" s="16" t="s">
+      <c r="S12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="R12" s="17" t="s">
+      <c r="T12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="S12" s="17" t="s">
+      <c r="U12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="T12" s="17" t="s">
+    </row>
+    <row r="13" ht="46" customHeight="1" spans="1:22">
+      <c r="A13" s="18">
+        <v>30</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>37</v>
       </c>
+      <c r="C13" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18">
+        <v>300</v>
+      </c>
+      <c r="F13" s="18">
+        <v>10</v>
+      </c>
+      <c r="G13" s="18">
+        <f t="shared" ref="G13:G18" si="0">E13*F13</f>
+        <v>3000</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18">
+        <v>50</v>
+      </c>
+      <c r="L13" s="18">
+        <v>45</v>
+      </c>
+      <c r="M13" s="18">
+        <v>60</v>
+      </c>
+      <c r="N13" s="18">
+        <v>20</v>
+      </c>
+      <c r="O13" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="P13" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="R13" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="U13" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="V13" s="19" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="13" ht="46" customHeight="1" spans="1:20">
-      <c r="A13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="18"/>
-    </row>
-    <row r="14" ht="46" customHeight="1" spans="1:20">
+    <row r="14" ht="46" customHeight="1" spans="1:22">
       <c r="A14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D14" s="18"/>
       <c r="E14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G14" s="18" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R14" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="R14" s="18" t="s">
+        <v>10</v>
+      </c>
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
     </row>
-    <row r="15" ht="46" customHeight="1" spans="1:20">
+    <row r="15" ht="46" customHeight="1" spans="1:22">
       <c r="A15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D15" s="18"/>
       <c r="E15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G15" s="18" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R15" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="R15" s="18" t="s">
+        <v>10</v>
+      </c>
       <c r="S15" s="18"/>
       <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
     </row>
-    <row r="16" ht="46" customHeight="1" spans="1:20">
+    <row r="16" ht="46" customHeight="1" spans="1:22">
       <c r="A16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D16" s="18"/>
       <c r="E16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G16" s="18" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R16" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="R16" s="18" t="s">
+        <v>10</v>
+      </c>
       <c r="S16" s="18"/>
       <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
     </row>
-    <row r="17" ht="46" customHeight="1" spans="1:20">
+    <row r="17" ht="46" customHeight="1" spans="1:21">
       <c r="A17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D17" s="18"/>
       <c r="E17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G17" s="18" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R17" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="R17" s="18" t="s">
+        <v>10</v>
+      </c>
       <c r="S17" s="18"/>
       <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
     </row>
-    <row r="18" ht="46" customHeight="1" spans="1:20">
+    <row r="18" ht="46" customHeight="1" spans="1:21">
       <c r="A18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D18" s="18"/>
       <c r="E18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G18" s="18" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R18" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="R18" s="18" t="s">
+        <v>10</v>
+      </c>
       <c r="S18" s="18"/>
       <c r="T18" s="18"/>
+      <c r="U18" s="18"/>
     </row>
-    <row r="19" ht="46" customHeight="1" spans="1:20">
-      <c r="A19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
+    <row r="19" ht="22" customHeight="1" spans="1:21">
+      <c r="A19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22">
+        <f>SUM(E13:E18)</f>
+        <v>300</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="23" t="e">
+        <f>SUM(G13:G18)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="46" customHeight="1" spans="1:20">
-      <c r="A20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
+    <row r="20" ht="22" customHeight="1" spans="1:21">
+      <c r="A20" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
     </row>
-    <row r="21" ht="46" customHeight="1" spans="1:20">
-      <c r="A21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
+    <row r="21" ht="22" customHeight="1" spans="1:21">
+      <c r="A21" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
     </row>
-    <row r="22" ht="46" customHeight="1" spans="1:20">
-      <c r="A22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-    </row>
-    <row r="23" ht="46" customHeight="1" spans="1:20">
-      <c r="A23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-    </row>
-    <row r="24" ht="46" customHeight="1" spans="1:20">
-      <c r="A24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18"/>
-    </row>
-    <row r="25" ht="46" customHeight="1" spans="1:20">
-      <c r="A25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R25" s="18"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="18"/>
-    </row>
-    <row r="26" ht="46" customHeight="1" spans="1:20">
-      <c r="A26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-    </row>
-    <row r="27" ht="46" customHeight="1" spans="1:20">
-      <c r="A27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="R27" s="18"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-    </row>
-    <row r="28" ht="22" customHeight="1" spans="1:20">
-      <c r="A28" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="21">
-        <f>SUM(E13:E27)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-    </row>
-    <row r="29" ht="22" customHeight="1" spans="1:20">
-      <c r="A29" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="1:20">
-      <c r="A30" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
-    </row>
-    <row r="32" ht="40" customHeight="1" spans="1:20">
-      <c r="A32" s="28" t="s">
-        <v>42</v>
+    <row r="23" ht="40" customHeight="1" spans="1:21">
+      <c r="A23" s="30" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K3:Q3"/>
+  <mergeCells count="38">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="L2:R2"/>
+    <mergeCell ref="L3:R3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:Q4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:Q5"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:R5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:Q6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:Q7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:Q8"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:R8"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:Q9"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:R9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:Q10"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:R10"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:Q11"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="F29:Q29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F30:Q30"/>
-    <mergeCell ref="A32:Q32"/>
-    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="G20:U20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="G21:U21"/>
+    <mergeCell ref="A23:R23"/>
     <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:E8"/>
+    <mergeCell ref="A2:K3"/>
+    <mergeCell ref="C7:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
